--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:38</t>
+    <t xml:space="preserve">2026-09-09 22:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:23</t>
+    <t xml:space="preserve">2026-09-12 19:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
@@ -36,70 +36,76 @@
     <t xml:space="preserve">Biobío</t>
   </si>
   <si>
+    <t xml:space="preserve">Concepción</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negrete</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hualpén</t>
   </si>
   <si>
-    <t xml:space="preserve">Concepción</t>
-  </si>
-  <si>
     <t xml:space="preserve">Florida</t>
   </si>
   <si>
+    <t xml:space="preserve">Quilaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contulmo</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Pedro de la Paz</t>
   </si>
   <si>
-    <t xml:space="preserve">Negrete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilaco</t>
+    <t xml:space="preserve">Hualqui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rosendo</t>
   </si>
   <si>
     <t xml:space="preserve">Chiguayante</t>
   </si>
   <si>
-    <t xml:space="preserve">Hualqui</t>
+    <t xml:space="preserve">Santa Juana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antuco</t>
   </si>
   <si>
     <t xml:space="preserve">Talcahuano</t>
   </si>
   <si>
-    <t xml:space="preserve">Contulmo</t>
+    <t xml:space="preserve">Yumbel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Bárbara</t>
   </si>
   <si>
     <t xml:space="preserve">Quilleco</t>
   </si>
   <si>
-    <t xml:space="preserve">Santa Bárbara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Juana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yumbel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rosendo</t>
+    <t xml:space="preserve">Alto Biobío</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirúa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Alamos</t>
   </si>
   <si>
     <t xml:space="preserve">Tucapel</t>
   </si>
   <si>
-    <t xml:space="preserve">Alto Biobío</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirúa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Laja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabrero</t>
   </si>
   <si>
     <t xml:space="preserve">Lota</t>
   </si>
   <si>
-    <t xml:space="preserve">Cabrero</t>
+    <t xml:space="preserve">Cañete</t>
   </si>
   <si>
     <t xml:space="preserve">Penco</t>
@@ -108,24 +114,18 @@
     <t xml:space="preserve">Coronel</t>
   </si>
   <si>
-    <t xml:space="preserve">Cañete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laja</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mulchén</t>
   </si>
   <si>
     <t xml:space="preserve">Tomé</t>
   </si>
   <si>
+    <t xml:space="preserve">Nacimiento</t>
+  </si>
+  <si>
     <t xml:space="preserve">Los Angeles</t>
   </si>
   <si>
-    <t xml:space="preserve">Nacimiento</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lebu</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:40</t>
+    <t xml:space="preserve">2026-09-24 00:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -574,13 +574,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8112</v>
+        <v>8101</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46.3</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="3">
@@ -591,13 +591,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8101</v>
+        <v>8307</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>45.74</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="4">
@@ -608,13 +608,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8104</v>
+        <v>8112</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>40.68</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="5">
@@ -625,13 +625,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>8108</v>
+        <v>8104</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>39.96</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="6">
@@ -642,13 +642,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8307</v>
+        <v>8308</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>38.9</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="7">
@@ -659,13 +659,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>8308</v>
+        <v>8204</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>36.25</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="8">
@@ -676,13 +676,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>8103</v>
+        <v>8108</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>35.45</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="9">
@@ -699,7 +699,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>35.07</v>
+        <v>16.27</v>
       </c>
     </row>
     <row r="10">
@@ -710,13 +710,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>8110</v>
+        <v>8310</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>35.01</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="11">
@@ -727,13 +727,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>8204</v>
+        <v>8103</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>32.98</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="12">
@@ -744,13 +744,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>8309</v>
+        <v>8109</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>32.44</v>
+        <v>15.29</v>
       </c>
     </row>
     <row r="13">
@@ -761,13 +761,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>8311</v>
+        <v>8302</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>32.36</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="14">
@@ -778,13 +778,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>8109</v>
+        <v>8110</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>32.25</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="15">
@@ -795,13 +795,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>8302</v>
+        <v>8313</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>31.88</v>
+        <v>14.67</v>
       </c>
     </row>
     <row r="16">
@@ -812,13 +812,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>8313</v>
+        <v>8311</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>31.04</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>8310</v>
+        <v>8309</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>30.83</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="18">
@@ -846,13 +846,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>8312</v>
+        <v>8314</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>29.93</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="19">
@@ -863,13 +863,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>8314</v>
+        <v>8207</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>29.49</v>
+        <v>14.06</v>
       </c>
     </row>
     <row r="20">
@@ -880,13 +880,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>8207</v>
+        <v>8206</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>28.46</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="21">
@@ -897,13 +897,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>8206</v>
+        <v>8312</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>28.42</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="22">
@@ -914,13 +914,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>8106</v>
+        <v>8304</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>28.26</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="23">
@@ -937,7 +937,7 @@
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>26.37</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="24">
@@ -948,13 +948,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>8107</v>
+        <v>8106</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>26.22</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="25">
@@ -965,13 +965,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>8102</v>
+        <v>8203</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>25.7</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="26">
@@ -982,13 +982,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>8203</v>
+        <v>8107</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>25.2</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="27">
@@ -999,13 +999,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>8304</v>
+        <v>8102</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>24.75</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="28">
@@ -1022,7 +1022,7 @@
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>23.21</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="29">
@@ -1039,7 +1039,7 @@
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>21.6</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="30">
@@ -1050,13 +1050,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>8301</v>
+        <v>8306</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>21.3</v>
+        <v>9.7</v>
       </c>
     </row>
     <row r="31">
@@ -1067,13 +1067,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>8306</v>
+        <v>8301</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>21.2</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="32">
@@ -1090,7 +1090,7 @@
         <v>2022</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>21.1</v>
+        <v>9.28</v>
       </c>
     </row>
     <row r="33">
@@ -1107,7 +1107,7 @@
         <v>2022</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>20.43</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="34">
@@ -1124,7 +1124,7 @@
         <v>2022</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>18.77</v>
+        <v>8.18</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:18</t>
+    <t xml:space="preserve">2026-09-27 22:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:07</t>
+    <t xml:space="preserve">2026-09-29 11:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -580,7 +580,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>19.82</v>
+        <v>198.17</v>
       </c>
     </row>
     <row r="3">
@@ -597,7 +597,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>18.39</v>
+        <v>183.93</v>
       </c>
     </row>
     <row r="4">
@@ -614,7 +614,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>18.39</v>
+        <v>183.87</v>
       </c>
     </row>
     <row r="5">
@@ -631,7 +631,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>18.37</v>
+        <v>183.73</v>
       </c>
     </row>
     <row r="6">
@@ -648,7 +648,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>17.76</v>
+        <v>177.57</v>
       </c>
     </row>
     <row r="7">
@@ -665,7 +665,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>17.43</v>
+        <v>174.34</v>
       </c>
     </row>
     <row r="8">
@@ -682,7 +682,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>17.12</v>
+        <v>171.24</v>
       </c>
     </row>
     <row r="9">
@@ -699,7 +699,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>16.27</v>
+        <v>162.71</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>15.57</v>
+        <v>155.72</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>15.42</v>
+        <v>154.23</v>
       </c>
     </row>
     <row r="12">
@@ -750,7 +750,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>15.29</v>
+        <v>152.91</v>
       </c>
     </row>
     <row r="13">
@@ -767,7 +767,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>15.08</v>
+        <v>150.82</v>
       </c>
     </row>
     <row r="14">
@@ -784,7 +784,7 @@
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15.08</v>
+        <v>150.82</v>
       </c>
     </row>
     <row r="15">
@@ -801,7 +801,7 @@
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>14.67</v>
+        <v>146.72</v>
       </c>
     </row>
     <row r="16">
@@ -818,7 +818,7 @@
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>14.54</v>
+        <v>145.42</v>
       </c>
     </row>
     <row r="17">
@@ -835,7 +835,7 @@
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>14.46</v>
+        <v>144.63</v>
       </c>
     </row>
     <row r="18">
@@ -852,7 +852,7 @@
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>14.19</v>
+        <v>141.88</v>
       </c>
     </row>
     <row r="19">
@@ -869,7 +869,7 @@
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>14.06</v>
+        <v>140.64</v>
       </c>
     </row>
     <row r="20">
@@ -886,7 +886,7 @@
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>13.97</v>
+        <v>139.73</v>
       </c>
     </row>
     <row r="21">
@@ -903,7 +903,7 @@
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>13.69</v>
+        <v>136.93</v>
       </c>
     </row>
     <row r="22">
@@ -920,7 +920,7 @@
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>12.33</v>
+        <v>123.3</v>
       </c>
     </row>
     <row r="23">
@@ -937,7 +937,7 @@
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>12.3</v>
+        <v>122.95</v>
       </c>
     </row>
     <row r="24">
@@ -954,7 +954,7 @@
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>12.17</v>
+        <v>121.75</v>
       </c>
     </row>
     <row r="25">
@@ -971,7 +971,7 @@
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>11.49</v>
+        <v>114.91</v>
       </c>
     </row>
     <row r="26">
@@ -988,7 +988,7 @@
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>11.49</v>
+        <v>114.9</v>
       </c>
     </row>
     <row r="27">
@@ -1005,7 +1005,7 @@
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>11.31</v>
+        <v>113.15</v>
       </c>
     </row>
     <row r="28">
@@ -1022,7 +1022,7 @@
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>10.91</v>
+        <v>109.12</v>
       </c>
     </row>
     <row r="29">
@@ -1039,7 +1039,7 @@
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>10.24</v>
+        <v>102.35</v>
       </c>
     </row>
     <row r="30">
@@ -1056,7 +1056,7 @@
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>9.7</v>
+        <v>96.98</v>
       </c>
     </row>
     <row r="31">
@@ -1073,7 +1073,7 @@
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>9.59</v>
+        <v>95.95</v>
       </c>
     </row>
     <row r="32">
@@ -1090,7 +1090,7 @@
         <v>2022</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>9.28</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="33">
@@ -1107,7 +1107,7 @@
         <v>2022</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>9.27</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="34">
@@ -1124,7 +1124,7 @@
         <v>2022</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>8.18</v>
+        <v>81.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:01</t>
+    <t xml:space="preserve">2026-10-01 19:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -162,7 +162,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:26</t>
+    <t xml:space="preserve">2026-10-02 13:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Tirúa</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Tucapel</t>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Nacimiento</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Lebu</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:07</t>
+    <t xml:space="preserve">2026-10-04 07:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 07:57</t>
+    <t xml:space="preserve">2026-10-05 07:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
